--- a/Cohorte IA/Programme_Cohorte_IA.xlsx
+++ b/Cohorte IA/Programme_Cohorte_IA.xlsx
@@ -1,14 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Julien\Cohorte IA\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5867976-8684-4D4E-8F0B-CD6EF94FE0B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Programme_Cohorte_IA" sheetId="1" r:id="rId5"/>
+    <sheet name="Programme_Cohorte_IA" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Programme_Cohorte_IA!$A$1:$M$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Programme_Cohorte_IA!$A$1:$M$36</definedName>
   </definedNames>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -549,118 +559,93 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="d mmmm"/>
+    <numFmt numFmtId="164" formatCode="d\ mmmm"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="12"/>
       <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
+      <sz val="12"/>
       <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <i/>
+      <sz val="12"/>
       <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <u/>
+      <sz val="12"/>
       <color rgb="FF0000FF"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <u/>
-      <color rgb="FF0000FF"/>
-    </font>
-    <font>
-      <u/>
-      <color rgb="FF0000FF"/>
-    </font>
-    <font>
-      <u/>
-      <color rgb="FF0000FF"/>
-    </font>
-    <font>
+      <sz val="12"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <color rgb="FFFFFFFF"/>
-    </font>
-    <font>
-      <u/>
-      <color rgb="FF0000FF"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
       <i/>
+      <sz val="12"/>
       <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
       <i/>
       <u/>
+      <sz val="12"/>
       <color rgb="FF0000FF"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <u/>
-      <color rgb="FF0000FF"/>
-    </font>
-    <font>
-      <b/>
-      <i/>
-      <u/>
-      <color rgb="FF0000FF"/>
-    </font>
-    <font>
-      <u/>
-      <color rgb="FF0000FF"/>
-    </font>
-    <font>
-      <u/>
-      <color rgb="FF0000FF"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
+      <sz val="12"/>
       <color rgb="FF000000"/>
-      <name val="-apple-system"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11.0"/>
-      <color rgb="FF000000"/>
-      <name val="-apple-system"/>
-    </font>
-    <font>
-      <u/>
-      <color rgb="FF0000FF"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="10">
@@ -668,7 +653,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -720,203 +705,97 @@
     </fill>
   </fills>
   <borders count="2">
-    <border/>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thick">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="4" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="4" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="5" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="5" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="5" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="5" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="6" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="6" fontId="9" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="6" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="6" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="6" fontId="9" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="7" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="7" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="7" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="7" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="7" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="13" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="13" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="8" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="8" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="8" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="8" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="8" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="16" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="9" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="9" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="9" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="9" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="9" fontId="17" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="9" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="9" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="9" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="9" fontId="19" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="9" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="4" fontId="21" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="6" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="6" fontId="9" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="6" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="6" fontId="9" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="6" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+  <cellXfs count="53">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="2" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="2" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="2" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{B8E9E935-879A-4A7E-B974-085A1F86B38C}"/>
+  </tableStyles>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -924,7 +803,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -1114,31 +993,36 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:AB46"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col customWidth="1" min="2" max="2" width="11.0"/>
-    <col customWidth="1" min="3" max="3" width="11.25"/>
-    <col customWidth="1" min="4" max="4" width="13.0"/>
-    <col customWidth="1" min="5" max="5" width="40.0"/>
-    <col customWidth="1" min="6" max="6" width="70.75"/>
-    <col customWidth="1" min="7" max="7" width="19.13"/>
-    <col customWidth="1" min="8" max="8" width="15.88"/>
-    <col customWidth="1" min="9" max="9" width="63.88"/>
-    <col customWidth="1" min="10" max="10" width="65.75"/>
-    <col customWidth="1" min="11" max="11" width="63.5"/>
-    <col customWidth="1" min="12" max="12" width="19.13"/>
-    <col customWidth="1" min="13" max="13" width="16.63"/>
+    <col min="1" max="1" width="12.5703125" style="3"/>
+    <col min="2" max="2" width="11" style="3" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="13" style="3" customWidth="1"/>
+    <col min="5" max="5" width="40" style="3" customWidth="1"/>
+    <col min="6" max="6" width="70.7109375" style="3" customWidth="1"/>
+    <col min="7" max="7" width="19.140625" style="3" customWidth="1"/>
+    <col min="8" max="8" width="15.85546875" style="3" customWidth="1"/>
+    <col min="9" max="9" width="63.85546875" style="3" customWidth="1"/>
+    <col min="10" max="10" width="65.7109375" style="3" customWidth="1"/>
+    <col min="11" max="11" width="63.42578125" style="3" customWidth="1"/>
+    <col min="12" max="12" width="19.140625" style="3" customWidth="1"/>
+    <col min="13" max="13" width="16.5703125" style="3" customWidth="1"/>
+    <col min="14" max="16384" width="12.5703125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1179,175 +1063,175 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="4">
-        <v>46251.0</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="C2" s="5">
+        <v>46251</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I2" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J2" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="K2" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="L2" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="M2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="7"/>
-      <c r="R2" s="7"/>
-      <c r="S2" s="7"/>
-      <c r="T2" s="7"/>
-      <c r="U2" s="7"/>
-      <c r="V2" s="7"/>
-      <c r="W2" s="7"/>
-      <c r="X2" s="7"/>
-      <c r="Y2" s="7"/>
-      <c r="Z2" s="7"/>
-      <c r="AA2" s="7"/>
-      <c r="AB2" s="7"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="s">
+      <c r="N2" s="4"/>
+      <c r="O2" s="4"/>
+      <c r="P2" s="4"/>
+      <c r="Q2" s="4"/>
+      <c r="R2" s="4"/>
+      <c r="S2" s="4"/>
+      <c r="T2" s="4"/>
+      <c r="U2" s="4"/>
+      <c r="V2" s="4"/>
+      <c r="W2" s="4"/>
+      <c r="X2" s="4"/>
+      <c r="Y2" s="4"/>
+      <c r="Z2" s="4"/>
+      <c r="AA2" s="4"/>
+      <c r="AB2" s="4"/>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="4">
-        <v>46252.0</v>
-      </c>
-      <c r="D3" s="3" t="s">
+      <c r="C3" s="5">
+        <v>46252</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="6" t="s">
         <v>24</v>
       </c>
       <c r="G3" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I3" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="K3" s="6" t="s">
+      <c r="K3" s="7" t="s">
         <v>20</v>
       </c>
       <c r="L3" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="M3" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="N3" s="7"/>
-      <c r="O3" s="7"/>
-      <c r="P3" s="7"/>
-      <c r="Q3" s="7"/>
-      <c r="R3" s="7"/>
-      <c r="S3" s="7"/>
-      <c r="T3" s="7"/>
-      <c r="U3" s="7"/>
-      <c r="V3" s="7"/>
-      <c r="W3" s="7"/>
-      <c r="X3" s="7"/>
-      <c r="Y3" s="7"/>
-      <c r="Z3" s="7"/>
-      <c r="AA3" s="7"/>
-      <c r="AB3" s="7"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="s">
+      <c r="N3" s="4"/>
+      <c r="O3" s="4"/>
+      <c r="P3" s="4"/>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="4"/>
+      <c r="S3" s="4"/>
+      <c r="T3" s="4"/>
+      <c r="U3" s="4"/>
+      <c r="V3" s="4"/>
+      <c r="W3" s="4"/>
+      <c r="X3" s="4"/>
+      <c r="Y3" s="4"/>
+      <c r="Z3" s="4"/>
+      <c r="AA3" s="4"/>
+      <c r="AB3" s="4"/>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="4">
-        <v>46253.0</v>
-      </c>
-      <c r="D4" s="3" t="s">
+      <c r="C4" s="5">
+        <v>46253</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H4" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="I4" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="J4" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="K4" s="6" t="s">
+      <c r="K4" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="L4" s="3" t="s">
+      <c r="L4" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="M4" s="3" t="s">
+      <c r="M4" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="N4" s="7"/>
-      <c r="O4" s="7"/>
-      <c r="P4" s="7"/>
-      <c r="Q4" s="7"/>
-      <c r="R4" s="7"/>
-      <c r="S4" s="7"/>
-      <c r="T4" s="7"/>
-      <c r="U4" s="7"/>
-      <c r="V4" s="7"/>
-      <c r="W4" s="7"/>
-      <c r="X4" s="7"/>
-      <c r="Y4" s="7"/>
-      <c r="Z4" s="7"/>
-      <c r="AA4" s="7"/>
-      <c r="AB4" s="7"/>
-    </row>
-    <row r="5">
+      <c r="N4" s="4"/>
+      <c r="O4" s="4"/>
+      <c r="P4" s="4"/>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="4"/>
+      <c r="S4" s="4"/>
+      <c r="T4" s="4"/>
+      <c r="U4" s="4"/>
+      <c r="V4" s="4"/>
+      <c r="W4" s="4"/>
+      <c r="X4" s="4"/>
+      <c r="Y4" s="4"/>
+      <c r="Z4" s="4"/>
+      <c r="AA4" s="4"/>
+      <c r="AB4" s="4"/>
+    </row>
+    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
         <v>11</v>
       </c>
@@ -1355,7 +1239,7 @@
         <v>34</v>
       </c>
       <c r="C5" s="10">
-        <v>46254.0</v>
+        <v>46254</v>
       </c>
       <c r="D5" s="9" t="s">
         <v>35</v>
@@ -1383,775 +1267,775 @@
       </c>
       <c r="L5" s="9"/>
       <c r="M5" s="9"/>
-      <c r="N5" s="13"/>
-      <c r="O5" s="13"/>
-      <c r="P5" s="13"/>
-      <c r="Q5" s="13"/>
-      <c r="R5" s="13"/>
-      <c r="S5" s="13"/>
-      <c r="T5" s="13"/>
-      <c r="U5" s="13"/>
-      <c r="V5" s="13"/>
-      <c r="W5" s="13"/>
-      <c r="X5" s="13"/>
-      <c r="Y5" s="13"/>
-      <c r="Z5" s="13"/>
-      <c r="AA5" s="13"/>
-      <c r="AB5" s="13"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="14" t="s">
+      <c r="N5" s="9"/>
+      <c r="O5" s="9"/>
+      <c r="P5" s="9"/>
+      <c r="Q5" s="9"/>
+      <c r="R5" s="9"/>
+      <c r="S5" s="9"/>
+      <c r="T5" s="9"/>
+      <c r="U5" s="9"/>
+      <c r="V5" s="9"/>
+      <c r="W5" s="9"/>
+      <c r="X5" s="9"/>
+      <c r="Y5" s="9"/>
+      <c r="Z5" s="9"/>
+      <c r="AA5" s="9"/>
+      <c r="AB5" s="9"/>
+    </row>
+    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A6" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C6" s="15">
-        <v>46255.0</v>
-      </c>
-      <c r="D6" s="14" t="s">
+      <c r="C6" s="14">
+        <v>46255</v>
+      </c>
+      <c r="D6" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="E6" s="14" t="s">
+      <c r="E6" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="F6" s="16" t="s">
+      <c r="F6" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="G6" s="14" t="s">
+      <c r="G6" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="H6" s="14" t="s">
+      <c r="H6" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="I6" s="17" t="s">
+      <c r="I6" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="J6" s="14" t="s">
+      <c r="J6" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="K6" s="17" t="s">
+      <c r="K6" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="L6" s="14"/>
-      <c r="M6" s="14"/>
-      <c r="N6" s="18"/>
-      <c r="O6" s="18"/>
-      <c r="P6" s="18"/>
-      <c r="Q6" s="18"/>
-      <c r="R6" s="18"/>
-      <c r="S6" s="18"/>
-      <c r="T6" s="18"/>
-      <c r="U6" s="18"/>
-      <c r="V6" s="18"/>
-      <c r="W6" s="18"/>
-      <c r="X6" s="18"/>
-      <c r="Y6" s="18"/>
-      <c r="Z6" s="18"/>
-      <c r="AA6" s="18"/>
-      <c r="AB6" s="18"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="19" t="s">
+      <c r="L6" s="13"/>
+      <c r="M6" s="13"/>
+      <c r="N6" s="13"/>
+      <c r="O6" s="13"/>
+      <c r="P6" s="13"/>
+      <c r="Q6" s="13"/>
+      <c r="R6" s="13"/>
+      <c r="S6" s="13"/>
+      <c r="T6" s="13"/>
+      <c r="U6" s="13"/>
+      <c r="V6" s="13"/>
+      <c r="W6" s="13"/>
+      <c r="X6" s="13"/>
+      <c r="Y6" s="13"/>
+      <c r="Z6" s="13"/>
+      <c r="AA6" s="13"/>
+      <c r="AB6" s="13"/>
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A7" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="20">
-        <v>46258.0</v>
-      </c>
-      <c r="D7" s="19" t="s">
+      <c r="C7" s="18">
+        <v>46258</v>
+      </c>
+      <c r="D7" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="E7" s="19" t="s">
+      <c r="E7" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="F7" s="21" t="s">
+      <c r="F7" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="G7" s="19" t="s">
+      <c r="G7" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="H7" s="19" t="s">
+      <c r="H7" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="I7" s="22" t="s">
+      <c r="I7" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="J7" s="19" t="s">
+      <c r="J7" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="K7" s="22" t="s">
+      <c r="K7" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="L7" s="19" t="s">
+      <c r="L7" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="M7" s="19" t="s">
+      <c r="M7" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="N7" s="23"/>
-      <c r="O7" s="23"/>
-      <c r="P7" s="23"/>
-      <c r="Q7" s="23"/>
-      <c r="R7" s="23"/>
-      <c r="S7" s="23"/>
-      <c r="T7" s="23"/>
-      <c r="U7" s="23"/>
-      <c r="V7" s="23"/>
-      <c r="W7" s="23"/>
-      <c r="X7" s="23"/>
-      <c r="Y7" s="23"/>
-      <c r="Z7" s="23"/>
-      <c r="AA7" s="23"/>
-      <c r="AB7" s="23"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="19" t="s">
+      <c r="N7" s="17"/>
+      <c r="O7" s="17"/>
+      <c r="P7" s="17"/>
+      <c r="Q7" s="17"/>
+      <c r="R7" s="17"/>
+      <c r="S7" s="17"/>
+      <c r="T7" s="17"/>
+      <c r="U7" s="17"/>
+      <c r="V7" s="17"/>
+      <c r="W7" s="17"/>
+      <c r="X7" s="17"/>
+      <c r="Y7" s="17"/>
+      <c r="Z7" s="17"/>
+      <c r="AA7" s="17"/>
+      <c r="AB7" s="17"/>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A8" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="20">
-        <v>46259.0</v>
-      </c>
-      <c r="D8" s="19" t="s">
+      <c r="C8" s="18">
+        <v>46259</v>
+      </c>
+      <c r="D8" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="E8" s="19" t="s">
+      <c r="E8" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="F8" s="21" t="s">
+      <c r="F8" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="G8" s="24" t="s">
+      <c r="G8" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="H8" s="19" t="s">
+      <c r="H8" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="I8" s="22" t="s">
+      <c r="I8" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="J8" s="19" t="s">
+      <c r="J8" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="K8" s="22" t="s">
+      <c r="K8" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="L8" s="19" t="s">
+      <c r="L8" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="M8" s="19" t="s">
+      <c r="M8" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="N8" s="23"/>
-      <c r="O8" s="23"/>
-      <c r="P8" s="23"/>
-      <c r="Q8" s="23"/>
-      <c r="R8" s="23"/>
-      <c r="S8" s="23"/>
-      <c r="T8" s="23"/>
-      <c r="U8" s="23"/>
-      <c r="V8" s="23"/>
-      <c r="W8" s="23"/>
-      <c r="X8" s="23"/>
-      <c r="Y8" s="23"/>
-      <c r="Z8" s="23"/>
-      <c r="AA8" s="23"/>
-      <c r="AB8" s="23"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="19" t="s">
+      <c r="N8" s="17"/>
+      <c r="O8" s="17"/>
+      <c r="P8" s="17"/>
+      <c r="Q8" s="17"/>
+      <c r="R8" s="17"/>
+      <c r="S8" s="17"/>
+      <c r="T8" s="17"/>
+      <c r="U8" s="17"/>
+      <c r="V8" s="17"/>
+      <c r="W8" s="17"/>
+      <c r="X8" s="17"/>
+      <c r="Y8" s="17"/>
+      <c r="Z8" s="17"/>
+      <c r="AA8" s="17"/>
+      <c r="AB8" s="17"/>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A9" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="20">
-        <v>46260.0</v>
-      </c>
-      <c r="D9" s="19" t="s">
+      <c r="C9" s="18">
+        <v>46260</v>
+      </c>
+      <c r="D9" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="E9" s="19" t="s">
+      <c r="E9" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="F9" s="21" t="s">
+      <c r="F9" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="G9" s="19" t="s">
+      <c r="G9" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="H9" s="19" t="s">
+      <c r="H9" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="I9" s="22" t="s">
+      <c r="I9" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="J9" s="19" t="s">
+      <c r="J9" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="K9" s="22" t="s">
+      <c r="K9" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="L9" s="19" t="s">
+      <c r="L9" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="M9" s="19" t="s">
+      <c r="M9" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="N9" s="23"/>
-      <c r="O9" s="23"/>
-      <c r="P9" s="23"/>
-      <c r="Q9" s="23"/>
-      <c r="R9" s="23"/>
-      <c r="S9" s="23"/>
-      <c r="T9" s="23"/>
-      <c r="U9" s="23"/>
-      <c r="V9" s="23"/>
-      <c r="W9" s="23"/>
-      <c r="X9" s="23"/>
-      <c r="Y9" s="23"/>
-      <c r="Z9" s="23"/>
-      <c r="AA9" s="23"/>
-      <c r="AB9" s="23"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="19" t="s">
+      <c r="N9" s="17"/>
+      <c r="O9" s="17"/>
+      <c r="P9" s="17"/>
+      <c r="Q9" s="17"/>
+      <c r="R9" s="17"/>
+      <c r="S9" s="17"/>
+      <c r="T9" s="17"/>
+      <c r="U9" s="17"/>
+      <c r="V9" s="17"/>
+      <c r="W9" s="17"/>
+      <c r="X9" s="17"/>
+      <c r="Y9" s="17"/>
+      <c r="Z9" s="17"/>
+      <c r="AA9" s="17"/>
+      <c r="AB9" s="17"/>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A10" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="C10" s="20">
-        <v>46261.0</v>
-      </c>
-      <c r="D10" s="19" t="s">
+      <c r="C10" s="18">
+        <v>46261</v>
+      </c>
+      <c r="D10" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="E10" s="19" t="s">
+      <c r="E10" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="F10" s="21" t="s">
+      <c r="F10" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="G10" s="19" t="s">
+      <c r="G10" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="H10" s="19" t="s">
+      <c r="H10" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="I10" s="22" t="s">
+      <c r="I10" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="J10" s="19" t="s">
+      <c r="J10" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="K10" s="22" t="s">
+      <c r="K10" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="L10" s="19" t="s">
+      <c r="L10" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="M10" s="19" t="s">
+      <c r="M10" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="N10" s="23"/>
-      <c r="O10" s="23"/>
-      <c r="P10" s="23"/>
-      <c r="Q10" s="23"/>
-      <c r="R10" s="23"/>
-      <c r="S10" s="23"/>
-      <c r="T10" s="23"/>
-      <c r="U10" s="23"/>
-      <c r="V10" s="23"/>
-      <c r="W10" s="23"/>
-      <c r="X10" s="23"/>
-      <c r="Y10" s="23"/>
-      <c r="Z10" s="23"/>
-      <c r="AA10" s="23"/>
-      <c r="AB10" s="23"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="25" t="s">
+      <c r="N10" s="17"/>
+      <c r="O10" s="17"/>
+      <c r="P10" s="17"/>
+      <c r="Q10" s="17"/>
+      <c r="R10" s="17"/>
+      <c r="S10" s="17"/>
+      <c r="T10" s="17"/>
+      <c r="U10" s="17"/>
+      <c r="V10" s="17"/>
+      <c r="W10" s="17"/>
+      <c r="X10" s="17"/>
+      <c r="Y10" s="17"/>
+      <c r="Z10" s="17"/>
+      <c r="AA10" s="17"/>
+      <c r="AB10" s="17"/>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A11" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="B11" s="25" t="s">
+      <c r="B11" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="C11" s="26">
-        <v>46262.0</v>
-      </c>
-      <c r="D11" s="25" t="s">
+      <c r="C11" s="23">
+        <v>46262</v>
+      </c>
+      <c r="D11" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="E11" s="25" t="s">
+      <c r="E11" s="22" t="s">
         <v>65</v>
       </c>
-      <c r="F11" s="27" t="s">
+      <c r="F11" s="24" t="s">
         <v>66</v>
       </c>
-      <c r="G11" s="25" t="s">
+      <c r="G11" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="H11" s="25"/>
-      <c r="I11" s="28" t="s">
+      <c r="H11" s="22"/>
+      <c r="I11" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="J11" s="25" t="s">
+      <c r="J11" s="22" t="s">
         <v>68</v>
       </c>
-      <c r="K11" s="28" t="s">
+      <c r="K11" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="L11" s="25" t="s">
+      <c r="L11" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="M11" s="25" t="s">
+      <c r="M11" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="N11" s="29"/>
-      <c r="O11" s="29"/>
-      <c r="P11" s="29"/>
-      <c r="Q11" s="29"/>
-      <c r="R11" s="29"/>
-      <c r="S11" s="29"/>
-      <c r="T11" s="29"/>
-      <c r="U11" s="29"/>
-      <c r="V11" s="29"/>
-      <c r="W11" s="29"/>
-      <c r="X11" s="29"/>
-      <c r="Y11" s="29"/>
-      <c r="Z11" s="29"/>
-      <c r="AA11" s="29"/>
-      <c r="AB11" s="29"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="30" t="s">
+      <c r="N11" s="22"/>
+      <c r="O11" s="22"/>
+      <c r="P11" s="22"/>
+      <c r="Q11" s="22"/>
+      <c r="R11" s="22"/>
+      <c r="S11" s="22"/>
+      <c r="T11" s="22"/>
+      <c r="U11" s="22"/>
+      <c r="V11" s="22"/>
+      <c r="W11" s="22"/>
+      <c r="X11" s="22"/>
+      <c r="Y11" s="22"/>
+      <c r="Z11" s="22"/>
+      <c r="AA11" s="22"/>
+      <c r="AB11" s="22"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A12" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="B12" s="30" t="s">
+      <c r="B12" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="31">
-        <v>46265.0</v>
-      </c>
-      <c r="D12" s="30" t="s">
+      <c r="C12" s="27">
+        <v>46265</v>
+      </c>
+      <c r="D12" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="E12" s="30" t="s">
+      <c r="E12" s="26" t="s">
         <v>72</v>
       </c>
-      <c r="F12" s="32" t="s">
+      <c r="F12" s="28" t="s">
         <v>73</v>
       </c>
-      <c r="G12" s="30" t="s">
+      <c r="G12" s="26" t="s">
         <v>74</v>
       </c>
-      <c r="H12" s="30" t="s">
+      <c r="H12" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="I12" s="33" t="s">
+      <c r="I12" s="29" t="s">
         <v>18</v>
       </c>
-      <c r="J12" s="30" t="s">
+      <c r="J12" s="26" t="s">
         <v>76</v>
       </c>
-      <c r="K12" s="33" t="s">
+      <c r="K12" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="L12" s="30"/>
-      <c r="M12" s="30"/>
-      <c r="N12" s="34"/>
-      <c r="O12" s="34"/>
-      <c r="P12" s="34"/>
-      <c r="Q12" s="34"/>
-      <c r="R12" s="34"/>
-      <c r="S12" s="34"/>
-      <c r="T12" s="34"/>
-      <c r="U12" s="34"/>
-      <c r="V12" s="34"/>
-      <c r="W12" s="34"/>
-      <c r="X12" s="34"/>
-      <c r="Y12" s="34"/>
-      <c r="Z12" s="34"/>
-      <c r="AA12" s="34"/>
-      <c r="AB12" s="34"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="30" t="s">
+      <c r="L12" s="26"/>
+      <c r="M12" s="26"/>
+      <c r="N12" s="26"/>
+      <c r="O12" s="26"/>
+      <c r="P12" s="26"/>
+      <c r="Q12" s="26"/>
+      <c r="R12" s="26"/>
+      <c r="S12" s="26"/>
+      <c r="T12" s="26"/>
+      <c r="U12" s="26"/>
+      <c r="V12" s="26"/>
+      <c r="W12" s="26"/>
+      <c r="X12" s="26"/>
+      <c r="Y12" s="26"/>
+      <c r="Z12" s="26"/>
+      <c r="AA12" s="26"/>
+      <c r="AB12" s="26"/>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A13" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="B13" s="30" t="s">
+      <c r="B13" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="C13" s="31">
-        <v>46266.0</v>
-      </c>
-      <c r="D13" s="30" t="s">
+      <c r="C13" s="27">
+        <v>46266</v>
+      </c>
+      <c r="D13" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="E13" s="30" t="s">
+      <c r="E13" s="26" t="s">
         <v>77</v>
       </c>
-      <c r="F13" s="32" t="s">
+      <c r="F13" s="28" t="s">
         <v>78</v>
       </c>
-      <c r="G13" s="30" t="s">
+      <c r="G13" s="26" t="s">
         <v>79</v>
       </c>
-      <c r="H13" s="30" t="s">
+      <c r="H13" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="I13" s="33" t="s">
+      <c r="I13" s="29" t="s">
         <v>18</v>
       </c>
-      <c r="J13" s="30" t="s">
+      <c r="J13" s="26" t="s">
         <v>80</v>
       </c>
-      <c r="K13" s="33" t="s">
+      <c r="K13" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="L13" s="30"/>
-      <c r="M13" s="30"/>
-      <c r="N13" s="34"/>
-      <c r="O13" s="34"/>
-      <c r="P13" s="34"/>
-      <c r="Q13" s="34"/>
-      <c r="R13" s="34"/>
-      <c r="S13" s="34"/>
-      <c r="T13" s="34"/>
-      <c r="U13" s="34"/>
-      <c r="V13" s="34"/>
-      <c r="W13" s="34"/>
-      <c r="X13" s="34"/>
-      <c r="Y13" s="34"/>
-      <c r="Z13" s="34"/>
-      <c r="AA13" s="34"/>
-      <c r="AB13" s="34"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="30" t="s">
+      <c r="L13" s="26"/>
+      <c r="M13" s="26"/>
+      <c r="N13" s="26"/>
+      <c r="O13" s="26"/>
+      <c r="P13" s="26"/>
+      <c r="Q13" s="26"/>
+      <c r="R13" s="26"/>
+      <c r="S13" s="26"/>
+      <c r="T13" s="26"/>
+      <c r="U13" s="26"/>
+      <c r="V13" s="26"/>
+      <c r="W13" s="26"/>
+      <c r="X13" s="26"/>
+      <c r="Y13" s="26"/>
+      <c r="Z13" s="26"/>
+      <c r="AA13" s="26"/>
+      <c r="AB13" s="26"/>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A14" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="B14" s="30" t="s">
+      <c r="B14" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="31">
-        <v>46267.0</v>
-      </c>
-      <c r="D14" s="30" t="s">
+      <c r="C14" s="27">
+        <v>46267</v>
+      </c>
+      <c r="D14" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="E14" s="30" t="s">
+      <c r="E14" s="26" t="s">
         <v>81</v>
       </c>
-      <c r="F14" s="32" t="s">
+      <c r="F14" s="28" t="s">
         <v>82</v>
       </c>
-      <c r="G14" s="30" t="s">
+      <c r="G14" s="26" t="s">
         <v>83</v>
       </c>
-      <c r="H14" s="30" t="s">
+      <c r="H14" s="26" t="s">
         <v>84</v>
       </c>
-      <c r="I14" s="33" t="s">
+      <c r="I14" s="29" t="s">
         <v>18</v>
       </c>
-      <c r="J14" s="30" t="s">
+      <c r="J14" s="26" t="s">
         <v>85</v>
       </c>
-      <c r="K14" s="33" t="s">
+      <c r="K14" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="L14" s="30"/>
-      <c r="M14" s="30"/>
-      <c r="N14" s="34"/>
-      <c r="O14" s="34"/>
-      <c r="P14" s="34"/>
-      <c r="Q14" s="34"/>
-      <c r="R14" s="34"/>
-      <c r="S14" s="34"/>
-      <c r="T14" s="34"/>
-      <c r="U14" s="34"/>
-      <c r="V14" s="34"/>
-      <c r="W14" s="34"/>
-      <c r="X14" s="34"/>
-      <c r="Y14" s="34"/>
-      <c r="Z14" s="34"/>
-      <c r="AA14" s="34"/>
-      <c r="AB14" s="34"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="30" t="s">
+      <c r="L14" s="26"/>
+      <c r="M14" s="26"/>
+      <c r="N14" s="26"/>
+      <c r="O14" s="26"/>
+      <c r="P14" s="26"/>
+      <c r="Q14" s="26"/>
+      <c r="R14" s="26"/>
+      <c r="S14" s="26"/>
+      <c r="T14" s="26"/>
+      <c r="U14" s="26"/>
+      <c r="V14" s="26"/>
+      <c r="W14" s="26"/>
+      <c r="X14" s="26"/>
+      <c r="Y14" s="26"/>
+      <c r="Z14" s="26"/>
+      <c r="AA14" s="26"/>
+      <c r="AB14" s="26"/>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A15" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="B15" s="30" t="s">
+      <c r="B15" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="C15" s="31">
-        <v>46268.0</v>
-      </c>
-      <c r="D15" s="30" t="s">
+      <c r="C15" s="27">
+        <v>46268</v>
+      </c>
+      <c r="D15" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="E15" s="30" t="s">
+      <c r="E15" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="F15" s="32" t="s">
+      <c r="F15" s="28" t="s">
         <v>87</v>
       </c>
-      <c r="G15" s="30" t="s">
+      <c r="G15" s="26" t="s">
         <v>88</v>
       </c>
-      <c r="H15" s="30" t="s">
+      <c r="H15" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="I15" s="33" t="s">
+      <c r="I15" s="29" t="s">
         <v>18</v>
       </c>
-      <c r="J15" s="30" t="s">
+      <c r="J15" s="26" t="s">
         <v>89</v>
       </c>
-      <c r="K15" s="33" t="s">
+      <c r="K15" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="L15" s="34"/>
-      <c r="M15" s="34"/>
-      <c r="N15" s="34"/>
-      <c r="O15" s="34"/>
-      <c r="P15" s="34"/>
-      <c r="Q15" s="34"/>
-      <c r="R15" s="34"/>
-      <c r="S15" s="34"/>
-      <c r="T15" s="34"/>
-      <c r="U15" s="34"/>
-      <c r="V15" s="34"/>
-      <c r="W15" s="34"/>
-      <c r="X15" s="34"/>
-      <c r="Y15" s="34"/>
-      <c r="Z15" s="34"/>
-      <c r="AA15" s="34"/>
-      <c r="AB15" s="34"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="35" t="s">
+      <c r="L15" s="26"/>
+      <c r="M15" s="26"/>
+      <c r="N15" s="26"/>
+      <c r="O15" s="26"/>
+      <c r="P15" s="26"/>
+      <c r="Q15" s="26"/>
+      <c r="R15" s="26"/>
+      <c r="S15" s="26"/>
+      <c r="T15" s="26"/>
+      <c r="U15" s="26"/>
+      <c r="V15" s="26"/>
+      <c r="W15" s="26"/>
+      <c r="X15" s="26"/>
+      <c r="Y15" s="26"/>
+      <c r="Z15" s="26"/>
+      <c r="AA15" s="26"/>
+      <c r="AB15" s="26"/>
+    </row>
+    <row r="16" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="30" t="s">
         <v>70</v>
       </c>
-      <c r="B16" s="35" t="s">
+      <c r="B16" s="30" t="s">
         <v>40</v>
       </c>
-      <c r="C16" s="36">
-        <v>46269.0</v>
-      </c>
-      <c r="D16" s="35"/>
-      <c r="E16" s="35" t="s">
+      <c r="C16" s="31">
+        <v>46269</v>
+      </c>
+      <c r="D16" s="30"/>
+      <c r="E16" s="30" t="s">
         <v>90</v>
       </c>
-      <c r="F16" s="35" t="s">
+      <c r="F16" s="30" t="s">
         <v>91</v>
       </c>
-      <c r="G16" s="37"/>
-      <c r="H16" s="35" t="s">
+      <c r="G16" s="30"/>
+      <c r="H16" s="30" t="s">
         <v>92</v>
       </c>
-      <c r="I16" s="38" t="s">
+      <c r="I16" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="J16" s="35" t="s">
+      <c r="J16" s="30" t="s">
         <v>93</v>
       </c>
-      <c r="K16" s="38" t="s">
+      <c r="K16" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="L16" s="37"/>
-      <c r="M16" s="35" t="s">
+      <c r="L16" s="30"/>
+      <c r="M16" s="30" t="s">
         <v>92</v>
       </c>
-      <c r="N16" s="37"/>
-      <c r="O16" s="37"/>
-      <c r="P16" s="37"/>
-      <c r="Q16" s="37"/>
-      <c r="R16" s="37"/>
-      <c r="S16" s="37"/>
-      <c r="T16" s="37"/>
-      <c r="U16" s="37"/>
-      <c r="V16" s="37"/>
-      <c r="W16" s="37"/>
-      <c r="X16" s="37"/>
-      <c r="Y16" s="37"/>
-      <c r="Z16" s="37"/>
-      <c r="AA16" s="37"/>
-      <c r="AB16" s="37"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="30" t="s">
+      <c r="N16" s="30"/>
+      <c r="O16" s="30"/>
+      <c r="P16" s="30"/>
+      <c r="Q16" s="30"/>
+      <c r="R16" s="30"/>
+      <c r="S16" s="30"/>
+      <c r="T16" s="30"/>
+      <c r="U16" s="30"/>
+      <c r="V16" s="30"/>
+      <c r="W16" s="30"/>
+      <c r="X16" s="30"/>
+      <c r="Y16" s="30"/>
+      <c r="Z16" s="30"/>
+      <c r="AA16" s="30"/>
+      <c r="AB16" s="30"/>
+    </row>
+    <row r="17" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A17" s="26" t="s">
         <v>94</v>
       </c>
-      <c r="B17" s="30" t="s">
+      <c r="B17" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="C17" s="31">
-        <v>46272.0</v>
-      </c>
-      <c r="D17" s="30" t="s">
+      <c r="C17" s="27">
+        <v>46272</v>
+      </c>
+      <c r="D17" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="E17" s="30" t="s">
+      <c r="E17" s="26" t="s">
         <v>95</v>
       </c>
-      <c r="F17" s="32" t="s">
+      <c r="F17" s="28" t="s">
         <v>96</v>
       </c>
-      <c r="G17" s="30"/>
-      <c r="H17" s="30"/>
-      <c r="I17" s="33" t="s">
+      <c r="G17" s="26"/>
+      <c r="H17" s="26"/>
+      <c r="I17" s="29" t="s">
         <v>18</v>
       </c>
-      <c r="J17" s="30" t="s">
+      <c r="J17" s="26" t="s">
         <v>97</v>
       </c>
-      <c r="K17" s="33" t="s">
+      <c r="K17" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="L17" s="30" t="s">
+      <c r="L17" s="26" t="s">
         <v>98</v>
       </c>
-      <c r="M17" s="30" t="s">
+      <c r="M17" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="N17" s="34"/>
-      <c r="O17" s="34"/>
-      <c r="P17" s="34"/>
-      <c r="Q17" s="34"/>
-      <c r="R17" s="34"/>
-      <c r="S17" s="34"/>
-      <c r="T17" s="34"/>
-      <c r="U17" s="34"/>
-      <c r="V17" s="34"/>
-      <c r="W17" s="34"/>
-      <c r="X17" s="34"/>
-      <c r="Y17" s="34"/>
-      <c r="Z17" s="34"/>
-      <c r="AA17" s="34"/>
-      <c r="AB17" s="34"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="39" t="s">
+      <c r="N17" s="26"/>
+      <c r="O17" s="26"/>
+      <c r="P17" s="26"/>
+      <c r="Q17" s="26"/>
+      <c r="R17" s="26"/>
+      <c r="S17" s="26"/>
+      <c r="T17" s="26"/>
+      <c r="U17" s="26"/>
+      <c r="V17" s="26"/>
+      <c r="W17" s="26"/>
+      <c r="X17" s="26"/>
+      <c r="Y17" s="26"/>
+      <c r="Z17" s="26"/>
+      <c r="AA17" s="26"/>
+      <c r="AB17" s="26"/>
+    </row>
+    <row r="18" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A18" s="33" t="s">
         <v>94</v>
       </c>
-      <c r="B18" s="39" t="s">
+      <c r="B18" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="C18" s="40">
-        <v>46273.0</v>
-      </c>
-      <c r="D18" s="39" t="s">
+      <c r="C18" s="34">
+        <v>46273</v>
+      </c>
+      <c r="D18" s="33" t="s">
         <v>99</v>
       </c>
-      <c r="E18" s="39" t="s">
+      <c r="E18" s="33" t="s">
         <v>100</v>
       </c>
-      <c r="F18" s="41" t="s">
+      <c r="F18" s="35" t="s">
         <v>101</v>
       </c>
-      <c r="G18" s="39" t="s">
+      <c r="G18" s="33" t="s">
         <v>98</v>
       </c>
-      <c r="H18" s="39" t="s">
+      <c r="H18" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="I18" s="42" t="s">
+      <c r="I18" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="J18" s="39" t="s">
+      <c r="J18" s="33" t="s">
         <v>102</v>
       </c>
-      <c r="K18" s="42" t="s">
+      <c r="K18" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="L18" s="39" t="s">
+      <c r="L18" s="33" t="s">
         <v>98</v>
       </c>
-      <c r="M18" s="39" t="s">
+      <c r="M18" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="N18" s="43"/>
-      <c r="O18" s="43"/>
-      <c r="P18" s="43"/>
-      <c r="Q18" s="43"/>
-      <c r="R18" s="43"/>
-      <c r="S18" s="43"/>
-      <c r="T18" s="43"/>
-      <c r="U18" s="43"/>
-      <c r="V18" s="43"/>
-      <c r="W18" s="43"/>
-      <c r="X18" s="43"/>
-      <c r="Y18" s="43"/>
-      <c r="Z18" s="43"/>
-      <c r="AA18" s="43"/>
-      <c r="AB18" s="43"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="39" t="s">
+      <c r="N18" s="33"/>
+      <c r="O18" s="33"/>
+      <c r="P18" s="33"/>
+      <c r="Q18" s="33"/>
+      <c r="R18" s="33"/>
+      <c r="S18" s="33"/>
+      <c r="T18" s="33"/>
+      <c r="U18" s="33"/>
+      <c r="V18" s="33"/>
+      <c r="W18" s="33"/>
+      <c r="X18" s="33"/>
+      <c r="Y18" s="33"/>
+      <c r="Z18" s="33"/>
+      <c r="AA18" s="33"/>
+      <c r="AB18" s="33"/>
+    </row>
+    <row r="19" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A19" s="33" t="s">
         <v>94</v>
       </c>
-      <c r="B19" s="39" t="s">
+      <c r="B19" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="C19" s="40">
-        <v>46274.0</v>
-      </c>
-      <c r="D19" s="39" t="s">
+      <c r="C19" s="34">
+        <v>46274</v>
+      </c>
+      <c r="D19" s="33" t="s">
         <v>99</v>
       </c>
-      <c r="E19" s="39" t="s">
+      <c r="E19" s="33" t="s">
         <v>103</v>
       </c>
-      <c r="F19" s="41" t="s">
+      <c r="F19" s="35" t="s">
         <v>104</v>
       </c>
-      <c r="G19" s="39" t="s">
+      <c r="G19" s="33" t="s">
         <v>105</v>
       </c>
-      <c r="H19" s="39" t="s">
+      <c r="H19" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="I19" s="42" t="s">
+      <c r="I19" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="J19" s="39" t="s">
+      <c r="J19" s="33" t="s">
         <v>106</v>
       </c>
-      <c r="K19" s="42" t="s">
+      <c r="K19" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="L19" s="39" t="s">
+      <c r="L19" s="33" t="s">
         <v>105</v>
       </c>
-      <c r="M19" s="39" t="s">
+      <c r="M19" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="N19" s="43"/>
-      <c r="O19" s="43"/>
-      <c r="P19" s="43"/>
-      <c r="Q19" s="43"/>
-      <c r="R19" s="43"/>
-      <c r="S19" s="43"/>
-      <c r="T19" s="43"/>
-      <c r="U19" s="43"/>
-      <c r="V19" s="43"/>
-      <c r="W19" s="43"/>
-      <c r="X19" s="43"/>
-      <c r="Y19" s="43"/>
-      <c r="Z19" s="43"/>
-      <c r="AA19" s="43"/>
-      <c r="AB19" s="43"/>
-    </row>
-    <row r="20">
+      <c r="N19" s="33"/>
+      <c r="O19" s="33"/>
+      <c r="P19" s="33"/>
+      <c r="Q19" s="33"/>
+      <c r="R19" s="33"/>
+      <c r="S19" s="33"/>
+      <c r="T19" s="33"/>
+      <c r="U19" s="33"/>
+      <c r="V19" s="33"/>
+      <c r="W19" s="33"/>
+      <c r="X19" s="33"/>
+      <c r="Y19" s="33"/>
+      <c r="Z19" s="33"/>
+      <c r="AA19" s="33"/>
+      <c r="AB19" s="33"/>
+    </row>
+    <row r="20" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
         <v>94</v>
       </c>
@@ -2159,7 +2043,7 @@
         <v>34</v>
       </c>
       <c r="C20" s="10">
-        <v>46275.0</v>
+        <v>46275</v>
       </c>
       <c r="D20" s="9" t="s">
         <v>35</v>
@@ -2191,607 +2075,607 @@
       <c r="M20" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="N20" s="13"/>
-      <c r="O20" s="13"/>
-      <c r="P20" s="13"/>
-      <c r="Q20" s="13"/>
-      <c r="R20" s="13"/>
-      <c r="S20" s="13"/>
-      <c r="T20" s="13"/>
-      <c r="U20" s="13"/>
-      <c r="V20" s="13"/>
-      <c r="W20" s="13"/>
-      <c r="X20" s="13"/>
-      <c r="Y20" s="13"/>
-      <c r="Z20" s="13"/>
-      <c r="AA20" s="13"/>
-      <c r="AB20" s="13"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="35" t="s">
+      <c r="N20" s="9"/>
+      <c r="O20" s="9"/>
+      <c r="P20" s="9"/>
+      <c r="Q20" s="9"/>
+      <c r="R20" s="9"/>
+      <c r="S20" s="9"/>
+      <c r="T20" s="9"/>
+      <c r="U20" s="9"/>
+      <c r="V20" s="9"/>
+      <c r="W20" s="9"/>
+      <c r="X20" s="9"/>
+      <c r="Y20" s="9"/>
+      <c r="Z20" s="9"/>
+      <c r="AA20" s="9"/>
+      <c r="AB20" s="9"/>
+    </row>
+    <row r="21" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="30" t="s">
         <v>94</v>
       </c>
-      <c r="B21" s="35" t="s">
+      <c r="B21" s="30" t="s">
         <v>40</v>
       </c>
-      <c r="C21" s="36">
-        <v>46276.0</v>
-      </c>
-      <c r="D21" s="35"/>
-      <c r="E21" s="35" t="s">
+      <c r="C21" s="31">
+        <v>46276</v>
+      </c>
+      <c r="D21" s="30"/>
+      <c r="E21" s="30" t="s">
         <v>111</v>
       </c>
-      <c r="F21" s="35" t="s">
+      <c r="F21" s="30" t="s">
         <v>112</v>
       </c>
-      <c r="G21" s="37"/>
-      <c r="H21" s="37"/>
-      <c r="I21" s="44" t="s">
+      <c r="G21" s="30"/>
+      <c r="H21" s="30"/>
+      <c r="I21" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="J21" s="35" t="s">
+      <c r="J21" s="30" t="s">
         <v>113</v>
       </c>
-      <c r="K21" s="38" t="s">
+      <c r="K21" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="L21" s="37"/>
-      <c r="M21" s="37"/>
-      <c r="N21" s="37"/>
-      <c r="O21" s="37"/>
-      <c r="P21" s="37"/>
-      <c r="Q21" s="37"/>
-      <c r="R21" s="37"/>
-      <c r="S21" s="37"/>
-      <c r="T21" s="37"/>
-      <c r="U21" s="37"/>
-      <c r="V21" s="37"/>
-      <c r="W21" s="37"/>
-      <c r="X21" s="37"/>
-      <c r="Y21" s="37"/>
-      <c r="Z21" s="37"/>
-      <c r="AA21" s="37"/>
-      <c r="AB21" s="37"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="39" t="s">
+      <c r="L21" s="30"/>
+      <c r="M21" s="30"/>
+      <c r="N21" s="30"/>
+      <c r="O21" s="30"/>
+      <c r="P21" s="30"/>
+      <c r="Q21" s="30"/>
+      <c r="R21" s="30"/>
+      <c r="S21" s="30"/>
+      <c r="T21" s="30"/>
+      <c r="U21" s="30"/>
+      <c r="V21" s="30"/>
+      <c r="W21" s="30"/>
+      <c r="X21" s="30"/>
+      <c r="Y21" s="30"/>
+      <c r="Z21" s="30"/>
+      <c r="AA21" s="30"/>
+      <c r="AB21" s="30"/>
+    </row>
+    <row r="22" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A22" s="33" t="s">
         <v>114</v>
       </c>
-      <c r="B22" s="39" t="s">
+      <c r="B22" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="C22" s="40">
-        <v>46279.0</v>
-      </c>
-      <c r="D22" s="39" t="s">
+      <c r="C22" s="34">
+        <v>46279</v>
+      </c>
+      <c r="D22" s="33" t="s">
         <v>99</v>
       </c>
-      <c r="E22" s="39" t="s">
+      <c r="E22" s="33" t="s">
         <v>115</v>
       </c>
-      <c r="F22" s="41" t="s">
+      <c r="F22" s="35" t="s">
         <v>116</v>
       </c>
-      <c r="G22" s="39" t="s">
+      <c r="G22" s="33" t="s">
         <v>117</v>
       </c>
-      <c r="H22" s="39" t="s">
+      <c r="H22" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="I22" s="42" t="s">
+      <c r="I22" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="J22" s="39" t="s">
+      <c r="J22" s="33" t="s">
         <v>118</v>
       </c>
-      <c r="K22" s="42" t="s">
+      <c r="K22" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="L22" s="39" t="s">
+      <c r="L22" s="33" t="s">
         <v>117</v>
       </c>
-      <c r="M22" s="39" t="s">
+      <c r="M22" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="N22" s="43"/>
-      <c r="O22" s="43"/>
-      <c r="P22" s="43"/>
-      <c r="Q22" s="43"/>
-      <c r="R22" s="43"/>
-      <c r="S22" s="43"/>
-      <c r="T22" s="43"/>
-      <c r="U22" s="43"/>
-      <c r="V22" s="43"/>
-      <c r="W22" s="43"/>
-      <c r="X22" s="43"/>
-      <c r="Y22" s="43"/>
-      <c r="Z22" s="43"/>
-      <c r="AA22" s="43"/>
-      <c r="AB22" s="43"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="39" t="s">
+      <c r="N22" s="33"/>
+      <c r="O22" s="33"/>
+      <c r="P22" s="33"/>
+      <c r="Q22" s="33"/>
+      <c r="R22" s="33"/>
+      <c r="S22" s="33"/>
+      <c r="T22" s="33"/>
+      <c r="U22" s="33"/>
+      <c r="V22" s="33"/>
+      <c r="W22" s="33"/>
+      <c r="X22" s="33"/>
+      <c r="Y22" s="33"/>
+      <c r="Z22" s="33"/>
+      <c r="AA22" s="33"/>
+      <c r="AB22" s="33"/>
+    </row>
+    <row r="23" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A23" s="33" t="s">
         <v>114</v>
       </c>
-      <c r="B23" s="39" t="s">
+      <c r="B23" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="C23" s="40">
-        <v>46280.0</v>
-      </c>
-      <c r="D23" s="39" t="s">
+      <c r="C23" s="34">
+        <v>46280</v>
+      </c>
+      <c r="D23" s="33" t="s">
         <v>99</v>
       </c>
-      <c r="E23" s="39" t="s">
+      <c r="E23" s="33" t="s">
         <v>119</v>
       </c>
-      <c r="F23" s="41" t="s">
+      <c r="F23" s="35" t="s">
         <v>120</v>
       </c>
-      <c r="G23" s="39" t="s">
+      <c r="G23" s="33" t="s">
         <v>121</v>
       </c>
-      <c r="H23" s="39" t="s">
+      <c r="H23" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="I23" s="42" t="s">
+      <c r="I23" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="J23" s="39" t="s">
+      <c r="J23" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="K23" s="42" t="s">
+      <c r="K23" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="L23" s="39" t="s">
+      <c r="L23" s="33" t="s">
         <v>121</v>
       </c>
-      <c r="M23" s="39" t="s">
+      <c r="M23" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="N23" s="43"/>
-      <c r="O23" s="43"/>
-      <c r="P23" s="43"/>
-      <c r="Q23" s="43"/>
-      <c r="R23" s="43"/>
-      <c r="S23" s="43"/>
-      <c r="T23" s="43"/>
-      <c r="U23" s="43"/>
-      <c r="V23" s="43"/>
-      <c r="W23" s="43"/>
-      <c r="X23" s="43"/>
-      <c r="Y23" s="43"/>
-      <c r="Z23" s="43"/>
-      <c r="AA23" s="43"/>
-      <c r="AB23" s="43"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="39" t="s">
+      <c r="N23" s="33"/>
+      <c r="O23" s="33"/>
+      <c r="P23" s="33"/>
+      <c r="Q23" s="33"/>
+      <c r="R23" s="33"/>
+      <c r="S23" s="33"/>
+      <c r="T23" s="33"/>
+      <c r="U23" s="33"/>
+      <c r="V23" s="33"/>
+      <c r="W23" s="33"/>
+      <c r="X23" s="33"/>
+      <c r="Y23" s="33"/>
+      <c r="Z23" s="33"/>
+      <c r="AA23" s="33"/>
+      <c r="AB23" s="33"/>
+    </row>
+    <row r="24" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A24" s="33" t="s">
         <v>114</v>
       </c>
-      <c r="B24" s="39" t="s">
+      <c r="B24" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="C24" s="40">
-        <v>46281.0</v>
-      </c>
-      <c r="D24" s="39" t="s">
+      <c r="C24" s="34">
+        <v>46281</v>
+      </c>
+      <c r="D24" s="33" t="s">
         <v>99</v>
       </c>
-      <c r="E24" s="39" t="s">
+      <c r="E24" s="33" t="s">
         <v>123</v>
       </c>
-      <c r="F24" s="41" t="s">
+      <c r="F24" s="35" t="s">
         <v>124</v>
       </c>
-      <c r="G24" s="39" t="s">
+      <c r="G24" s="33" t="s">
         <v>125</v>
       </c>
-      <c r="H24" s="39" t="s">
+      <c r="H24" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="I24" s="42" t="s">
+      <c r="I24" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="J24" s="39" t="s">
+      <c r="J24" s="33" t="s">
         <v>126</v>
       </c>
-      <c r="K24" s="42" t="s">
+      <c r="K24" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="L24" s="39" t="s">
+      <c r="L24" s="33" t="s">
         <v>125</v>
       </c>
-      <c r="M24" s="39" t="s">
+      <c r="M24" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="N24" s="43"/>
-      <c r="O24" s="43"/>
-      <c r="P24" s="43"/>
-      <c r="Q24" s="43"/>
-      <c r="R24" s="43"/>
-      <c r="S24" s="43"/>
-      <c r="T24" s="43"/>
-      <c r="U24" s="43"/>
-      <c r="V24" s="43"/>
-      <c r="W24" s="43"/>
-      <c r="X24" s="43"/>
-      <c r="Y24" s="43"/>
-      <c r="Z24" s="43"/>
-      <c r="AA24" s="43"/>
-      <c r="AB24" s="43"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="39" t="s">
+      <c r="N24" s="33"/>
+      <c r="O24" s="33"/>
+      <c r="P24" s="33"/>
+      <c r="Q24" s="33"/>
+      <c r="R24" s="33"/>
+      <c r="S24" s="33"/>
+      <c r="T24" s="33"/>
+      <c r="U24" s="33"/>
+      <c r="V24" s="33"/>
+      <c r="W24" s="33"/>
+      <c r="X24" s="33"/>
+      <c r="Y24" s="33"/>
+      <c r="Z24" s="33"/>
+      <c r="AA24" s="33"/>
+      <c r="AB24" s="33"/>
+    </row>
+    <row r="25" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A25" s="33" t="s">
         <v>114</v>
       </c>
-      <c r="B25" s="39" t="s">
+      <c r="B25" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="C25" s="40">
-        <v>46282.0</v>
-      </c>
-      <c r="D25" s="39" t="s">
+      <c r="C25" s="34">
+        <v>46282</v>
+      </c>
+      <c r="D25" s="33" t="s">
         <v>99</v>
       </c>
-      <c r="E25" s="39" t="s">
+      <c r="E25" s="33" t="s">
         <v>127</v>
       </c>
-      <c r="F25" s="41" t="s">
+      <c r="F25" s="35" t="s">
         <v>128</v>
       </c>
-      <c r="G25" s="39" t="s">
+      <c r="G25" s="33" t="s">
         <v>129</v>
       </c>
-      <c r="H25" s="39" t="s">
+      <c r="H25" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="I25" s="42" t="s">
+      <c r="I25" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="J25" s="39" t="s">
+      <c r="J25" s="33" t="s">
         <v>130</v>
       </c>
-      <c r="K25" s="42" t="s">
+      <c r="K25" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="L25" s="39" t="s">
+      <c r="L25" s="33" t="s">
         <v>129</v>
       </c>
-      <c r="M25" s="39" t="s">
+      <c r="M25" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="N25" s="43"/>
-      <c r="O25" s="43"/>
-      <c r="P25" s="43"/>
-      <c r="Q25" s="43"/>
-      <c r="R25" s="43"/>
-      <c r="S25" s="43"/>
-      <c r="T25" s="43"/>
-      <c r="U25" s="43"/>
-      <c r="V25" s="43"/>
-      <c r="W25" s="43"/>
-      <c r="X25" s="43"/>
-      <c r="Y25" s="43"/>
-      <c r="Z25" s="43"/>
-      <c r="AA25" s="43"/>
-      <c r="AB25" s="43"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="35" t="s">
+      <c r="N25" s="33"/>
+      <c r="O25" s="33"/>
+      <c r="P25" s="33"/>
+      <c r="Q25" s="33"/>
+      <c r="R25" s="33"/>
+      <c r="S25" s="33"/>
+      <c r="T25" s="33"/>
+      <c r="U25" s="33"/>
+      <c r="V25" s="33"/>
+      <c r="W25" s="33"/>
+      <c r="X25" s="33"/>
+      <c r="Y25" s="33"/>
+      <c r="Z25" s="33"/>
+      <c r="AA25" s="33"/>
+      <c r="AB25" s="33"/>
+    </row>
+    <row r="26" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="30" t="s">
         <v>114</v>
       </c>
-      <c r="B26" s="35" t="s">
+      <c r="B26" s="30" t="s">
         <v>40</v>
       </c>
-      <c r="C26" s="36">
-        <v>46283.0</v>
-      </c>
-      <c r="D26" s="35"/>
-      <c r="E26" s="35" t="s">
+      <c r="C26" s="31">
+        <v>46283</v>
+      </c>
+      <c r="D26" s="30"/>
+      <c r="E26" s="30" t="s">
         <v>131</v>
       </c>
-      <c r="F26" s="35" t="s">
+      <c r="F26" s="30" t="s">
         <v>132</v>
       </c>
-      <c r="G26" s="37"/>
-      <c r="H26" s="37"/>
-      <c r="I26" s="44" t="s">
+      <c r="G26" s="30"/>
+      <c r="H26" s="30"/>
+      <c r="I26" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="J26" s="35" t="s">
+      <c r="J26" s="30" t="s">
         <v>133</v>
       </c>
-      <c r="K26" s="38" t="s">
+      <c r="K26" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="L26" s="37"/>
-      <c r="M26" s="37"/>
-      <c r="N26" s="37"/>
-      <c r="O26" s="37"/>
-      <c r="P26" s="37"/>
-      <c r="Q26" s="37"/>
-      <c r="R26" s="37"/>
-      <c r="S26" s="37"/>
-      <c r="T26" s="37"/>
-      <c r="U26" s="37"/>
-      <c r="V26" s="37"/>
-      <c r="W26" s="37"/>
-      <c r="X26" s="37"/>
-      <c r="Y26" s="37"/>
-      <c r="Z26" s="37"/>
-      <c r="AA26" s="37"/>
-      <c r="AB26" s="37"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="45" t="s">
+      <c r="L26" s="30"/>
+      <c r="M26" s="30"/>
+      <c r="N26" s="30"/>
+      <c r="O26" s="30"/>
+      <c r="P26" s="30"/>
+      <c r="Q26" s="30"/>
+      <c r="R26" s="30"/>
+      <c r="S26" s="30"/>
+      <c r="T26" s="30"/>
+      <c r="U26" s="30"/>
+      <c r="V26" s="30"/>
+      <c r="W26" s="30"/>
+      <c r="X26" s="30"/>
+      <c r="Y26" s="30"/>
+      <c r="Z26" s="30"/>
+      <c r="AA26" s="30"/>
+      <c r="AB26" s="30"/>
+    </row>
+    <row r="27" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A27" s="37" t="s">
         <v>134</v>
       </c>
-      <c r="B27" s="45" t="s">
+      <c r="B27" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="C27" s="46">
-        <v>46286.0</v>
-      </c>
-      <c r="D27" s="45" t="s">
+      <c r="C27" s="38">
+        <v>46286</v>
+      </c>
+      <c r="D27" s="37" t="s">
         <v>135</v>
       </c>
-      <c r="E27" s="45" t="s">
+      <c r="E27" s="37" t="s">
         <v>136</v>
       </c>
-      <c r="F27" s="47" t="s">
+      <c r="F27" s="39" t="s">
         <v>137</v>
       </c>
-      <c r="G27" s="48"/>
-      <c r="H27" s="48"/>
-      <c r="I27" s="49" t="s">
+      <c r="G27" s="37"/>
+      <c r="H27" s="37"/>
+      <c r="I27" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="J27" s="45" t="s">
+      <c r="J27" s="37" t="s">
         <v>138</v>
       </c>
-      <c r="K27" s="50" t="s">
+      <c r="K27" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="L27" s="51" t="s">
+      <c r="L27" s="41" t="s">
         <v>139</v>
       </c>
-      <c r="M27" s="51" t="s">
+      <c r="M27" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="N27" s="48"/>
-      <c r="O27" s="48"/>
-      <c r="P27" s="48"/>
-      <c r="Q27" s="48"/>
-      <c r="R27" s="48"/>
-      <c r="S27" s="48"/>
-      <c r="T27" s="48"/>
-      <c r="U27" s="48"/>
-      <c r="V27" s="48"/>
-      <c r="W27" s="48"/>
-      <c r="X27" s="48"/>
-      <c r="Y27" s="48"/>
-      <c r="Z27" s="48"/>
-      <c r="AA27" s="48"/>
-      <c r="AB27" s="48"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="45" t="s">
+      <c r="N27" s="37"/>
+      <c r="O27" s="37"/>
+      <c r="P27" s="37"/>
+      <c r="Q27" s="37"/>
+      <c r="R27" s="37"/>
+      <c r="S27" s="37"/>
+      <c r="T27" s="37"/>
+      <c r="U27" s="37"/>
+      <c r="V27" s="37"/>
+      <c r="W27" s="37"/>
+      <c r="X27" s="37"/>
+      <c r="Y27" s="37"/>
+      <c r="Z27" s="37"/>
+      <c r="AA27" s="37"/>
+      <c r="AB27" s="37"/>
+    </row>
+    <row r="28" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A28" s="37" t="s">
         <v>134</v>
       </c>
-      <c r="B28" s="45" t="s">
+      <c r="B28" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="C28" s="46">
-        <v>46287.0</v>
-      </c>
-      <c r="D28" s="45" t="s">
+      <c r="C28" s="38">
+        <v>46287</v>
+      </c>
+      <c r="D28" s="37" t="s">
         <v>135</v>
       </c>
-      <c r="E28" s="45" t="s">
+      <c r="E28" s="37" t="s">
         <v>140</v>
       </c>
-      <c r="F28" s="47" t="s">
+      <c r="F28" s="39" t="s">
         <v>141</v>
       </c>
-      <c r="G28" s="48"/>
-      <c r="H28" s="48"/>
-      <c r="I28" s="49" t="s">
+      <c r="G28" s="37"/>
+      <c r="H28" s="37"/>
+      <c r="I28" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="J28" s="45" t="s">
+      <c r="J28" s="37" t="s">
         <v>142</v>
       </c>
-      <c r="K28" s="50" t="s">
+      <c r="K28" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="L28" s="51" t="s">
+      <c r="L28" s="41" t="s">
         <v>143</v>
       </c>
-      <c r="M28" s="51" t="s">
+      <c r="M28" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="N28" s="48"/>
-      <c r="O28" s="48"/>
-      <c r="P28" s="48"/>
-      <c r="Q28" s="48"/>
-      <c r="R28" s="48"/>
-      <c r="S28" s="48"/>
-      <c r="T28" s="48"/>
-      <c r="U28" s="48"/>
-      <c r="V28" s="48"/>
-      <c r="W28" s="48"/>
-      <c r="X28" s="48"/>
-      <c r="Y28" s="48"/>
-      <c r="Z28" s="48"/>
-      <c r="AA28" s="48"/>
-      <c r="AB28" s="48"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="45" t="s">
+      <c r="N28" s="37"/>
+      <c r="O28" s="37"/>
+      <c r="P28" s="37"/>
+      <c r="Q28" s="37"/>
+      <c r="R28" s="37"/>
+      <c r="S28" s="37"/>
+      <c r="T28" s="37"/>
+      <c r="U28" s="37"/>
+      <c r="V28" s="37"/>
+      <c r="W28" s="37"/>
+      <c r="X28" s="37"/>
+      <c r="Y28" s="37"/>
+      <c r="Z28" s="37"/>
+      <c r="AA28" s="37"/>
+      <c r="AB28" s="37"/>
+    </row>
+    <row r="29" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A29" s="37" t="s">
         <v>134</v>
       </c>
-      <c r="B29" s="45" t="s">
+      <c r="B29" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="C29" s="46">
-        <v>46288.0</v>
-      </c>
-      <c r="D29" s="45" t="s">
+      <c r="C29" s="38">
+        <v>46288</v>
+      </c>
+      <c r="D29" s="37" t="s">
         <v>135</v>
       </c>
-      <c r="E29" s="45" t="s">
+      <c r="E29" s="37" t="s">
         <v>144</v>
       </c>
-      <c r="F29" s="47" t="s">
+      <c r="F29" s="39" t="s">
         <v>145</v>
       </c>
-      <c r="G29" s="48"/>
-      <c r="H29" s="48"/>
-      <c r="I29" s="49" t="s">
+      <c r="G29" s="37"/>
+      <c r="H29" s="37"/>
+      <c r="I29" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="J29" s="45" t="s">
+      <c r="J29" s="37" t="s">
         <v>146</v>
       </c>
-      <c r="K29" s="50" t="s">
+      <c r="K29" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="L29" s="51" t="s">
+      <c r="L29" s="41" t="s">
         <v>143</v>
       </c>
-      <c r="M29" s="51" t="s">
+      <c r="M29" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="N29" s="48"/>
-      <c r="O29" s="48"/>
-      <c r="P29" s="48"/>
-      <c r="Q29" s="48"/>
-      <c r="R29" s="48"/>
-      <c r="S29" s="48"/>
-      <c r="T29" s="48"/>
-      <c r="U29" s="48"/>
-      <c r="V29" s="48"/>
-      <c r="W29" s="48"/>
-      <c r="X29" s="48"/>
-      <c r="Y29" s="48"/>
-      <c r="Z29" s="48"/>
-      <c r="AA29" s="48"/>
-      <c r="AB29" s="48"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="45" t="s">
+      <c r="N29" s="37"/>
+      <c r="O29" s="37"/>
+      <c r="P29" s="37"/>
+      <c r="Q29" s="37"/>
+      <c r="R29" s="37"/>
+      <c r="S29" s="37"/>
+      <c r="T29" s="37"/>
+      <c r="U29" s="37"/>
+      <c r="V29" s="37"/>
+      <c r="W29" s="37"/>
+      <c r="X29" s="37"/>
+      <c r="Y29" s="37"/>
+      <c r="Z29" s="37"/>
+      <c r="AA29" s="37"/>
+      <c r="AB29" s="37"/>
+    </row>
+    <row r="30" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="37" t="s">
         <v>134</v>
       </c>
-      <c r="B30" s="45" t="s">
+      <c r="B30" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="C30" s="46">
-        <v>46289.0</v>
-      </c>
-      <c r="D30" s="45" t="s">
+      <c r="C30" s="38">
+        <v>46289</v>
+      </c>
+      <c r="D30" s="37" t="s">
         <v>135</v>
       </c>
-      <c r="E30" s="52" t="s">
+      <c r="E30" s="41" t="s">
         <v>147</v>
       </c>
-      <c r="F30" s="45" t="s">
+      <c r="F30" s="37" t="s">
         <v>148</v>
       </c>
-      <c r="G30" s="45" t="s">
+      <c r="G30" s="37" t="s">
         <v>149</v>
       </c>
-      <c r="H30" s="53" t="s">
+      <c r="H30" s="41" t="s">
         <v>150</v>
       </c>
-      <c r="I30" s="54" t="s">
+      <c r="I30" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="J30" s="45" t="s">
+      <c r="J30" s="37" t="s">
         <v>151</v>
       </c>
-      <c r="K30" s="50" t="s">
+      <c r="K30" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="L30" s="51" t="s">
+      <c r="L30" s="41" t="s">
         <v>139</v>
       </c>
-      <c r="M30" s="51" t="s">
+      <c r="M30" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="N30" s="48"/>
-      <c r="O30" s="48"/>
-      <c r="P30" s="48"/>
-      <c r="Q30" s="48"/>
-      <c r="R30" s="48"/>
-      <c r="S30" s="48"/>
-      <c r="T30" s="48"/>
-      <c r="U30" s="48"/>
-      <c r="V30" s="48"/>
-      <c r="W30" s="48"/>
-      <c r="X30" s="48"/>
-      <c r="Y30" s="48"/>
-      <c r="Z30" s="48"/>
-      <c r="AA30" s="48"/>
-      <c r="AB30" s="48"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="14" t="s">
+      <c r="N30" s="37"/>
+      <c r="O30" s="37"/>
+      <c r="P30" s="37"/>
+      <c r="Q30" s="37"/>
+      <c r="R30" s="37"/>
+      <c r="S30" s="37"/>
+      <c r="T30" s="37"/>
+      <c r="U30" s="37"/>
+      <c r="V30" s="37"/>
+      <c r="W30" s="37"/>
+      <c r="X30" s="37"/>
+      <c r="Y30" s="37"/>
+      <c r="Z30" s="37"/>
+      <c r="AA30" s="37"/>
+      <c r="AB30" s="37"/>
+    </row>
+    <row r="31" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A31" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="B31" s="14" t="s">
+      <c r="B31" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C31" s="15">
-        <v>46290.0</v>
-      </c>
-      <c r="D31" s="14" t="s">
+      <c r="C31" s="14">
+        <v>46290</v>
+      </c>
+      <c r="D31" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="E31" s="14" t="s">
+      <c r="E31" s="13" t="s">
         <v>152</v>
       </c>
-      <c r="F31" s="16" t="s">
+      <c r="F31" s="15" t="s">
         <v>153</v>
       </c>
-      <c r="G31" s="18"/>
-      <c r="H31" s="18"/>
-      <c r="I31" s="55" t="s">
+      <c r="G31" s="13"/>
+      <c r="H31" s="13"/>
+      <c r="I31" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="J31" s="14" t="s">
+      <c r="J31" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="K31" s="17" t="s">
+      <c r="K31" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="L31" s="18"/>
-      <c r="M31" s="18"/>
-      <c r="N31" s="18"/>
-      <c r="O31" s="18"/>
-      <c r="P31" s="18"/>
-      <c r="Q31" s="18"/>
-      <c r="R31" s="18"/>
-      <c r="S31" s="18"/>
-      <c r="T31" s="18"/>
-      <c r="U31" s="18"/>
-      <c r="V31" s="18"/>
-      <c r="W31" s="18"/>
-      <c r="X31" s="18"/>
-      <c r="Y31" s="18"/>
-      <c r="Z31" s="18"/>
-      <c r="AA31" s="18"/>
-      <c r="AB31" s="18"/>
-    </row>
-    <row r="32">
+      <c r="L31" s="13"/>
+      <c r="M31" s="13"/>
+      <c r="N31" s="13"/>
+      <c r="O31" s="13"/>
+      <c r="P31" s="13"/>
+      <c r="Q31" s="13"/>
+      <c r="R31" s="13"/>
+      <c r="S31" s="13"/>
+      <c r="T31" s="13"/>
+      <c r="U31" s="13"/>
+      <c r="V31" s="13"/>
+      <c r="W31" s="13"/>
+      <c r="X31" s="13"/>
+      <c r="Y31" s="13"/>
+      <c r="Z31" s="13"/>
+      <c r="AA31" s="13"/>
+      <c r="AB31" s="13"/>
+    </row>
+    <row r="32" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>155</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C32" s="56">
-        <v>46293.0</v>
+      <c r="C32" s="43">
+        <v>46293</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>156</v>
@@ -2799,22 +2683,22 @@
       <c r="E32" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="F32" s="57" t="s">
+      <c r="F32" s="44" t="s">
         <v>158</v>
       </c>
       <c r="J32" s="2" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>155</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C33" s="56">
-        <v>46294.0</v>
+      <c r="C33" s="43">
+        <v>46294</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>156</v>
@@ -2822,22 +2706,22 @@
       <c r="E33" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="F33" s="57" t="s">
+      <c r="F33" s="44" t="s">
         <v>158</v>
       </c>
       <c r="J33" s="2" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>155</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C34" s="56">
-        <v>46295.0</v>
+      <c r="C34" s="43">
+        <v>46295</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>156</v>
@@ -2845,142 +2729,142 @@
       <c r="E34" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="F34" s="57" t="s">
+      <c r="F34" s="44" t="s">
         <v>158</v>
       </c>
       <c r="J34" s="2" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="58" t="s">
+    <row r="35" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A35" s="45" t="s">
         <v>155</v>
       </c>
-      <c r="B35" s="58" t="s">
+      <c r="B35" s="45" t="s">
         <v>34</v>
       </c>
-      <c r="C35" s="59">
-        <v>46296.0</v>
-      </c>
-      <c r="D35" s="58" t="s">
+      <c r="C35" s="46">
+        <v>46296</v>
+      </c>
+      <c r="D35" s="45" t="s">
         <v>64</v>
       </c>
-      <c r="E35" s="58" t="s">
+      <c r="E35" s="45" t="s">
         <v>162</v>
       </c>
-      <c r="F35" s="60" t="s">
+      <c r="F35" s="47" t="s">
         <v>163</v>
       </c>
-      <c r="G35" s="61"/>
-      <c r="H35" s="61"/>
-      <c r="I35" s="61"/>
-      <c r="J35" s="58" t="s">
+      <c r="G35" s="45"/>
+      <c r="H35" s="45"/>
+      <c r="I35" s="45"/>
+      <c r="J35" s="45" t="s">
         <v>164</v>
       </c>
-      <c r="K35" s="61"/>
-      <c r="L35" s="61"/>
-      <c r="M35" s="61"/>
-      <c r="N35" s="61"/>
-      <c r="O35" s="61"/>
-      <c r="P35" s="61"/>
-      <c r="Q35" s="61"/>
-      <c r="R35" s="61"/>
-      <c r="S35" s="61"/>
-      <c r="T35" s="61"/>
-      <c r="U35" s="61"/>
-      <c r="V35" s="61"/>
-      <c r="W35" s="61"/>
-      <c r="X35" s="61"/>
-      <c r="Y35" s="61"/>
-      <c r="Z35" s="61"/>
-      <c r="AA35" s="61"/>
-      <c r="AB35" s="61"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="62" t="s">
+      <c r="K35" s="45"/>
+      <c r="L35" s="45"/>
+      <c r="M35" s="45"/>
+      <c r="N35" s="45"/>
+      <c r="O35" s="45"/>
+      <c r="P35" s="45"/>
+      <c r="Q35" s="45"/>
+      <c r="R35" s="45"/>
+      <c r="S35" s="45"/>
+      <c r="T35" s="45"/>
+      <c r="U35" s="45"/>
+      <c r="V35" s="45"/>
+      <c r="W35" s="45"/>
+      <c r="X35" s="45"/>
+      <c r="Y35" s="45"/>
+      <c r="Z35" s="45"/>
+      <c r="AA35" s="45"/>
+      <c r="AB35" s="45"/>
+    </row>
+    <row r="36" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A36" s="48" t="s">
         <v>155</v>
       </c>
-      <c r="B36" s="62" t="s">
+      <c r="B36" s="48" t="s">
         <v>40</v>
       </c>
-      <c r="C36" s="63">
-        <v>46297.0</v>
-      </c>
-      <c r="D36" s="62" t="s">
+      <c r="C36" s="49">
+        <v>46297</v>
+      </c>
+      <c r="D36" s="48" t="s">
         <v>156</v>
       </c>
-      <c r="E36" s="62" t="s">
+      <c r="E36" s="48" t="s">
         <v>165</v>
       </c>
-      <c r="F36" s="64" t="s">
+      <c r="F36" s="50" t="s">
         <v>166</v>
       </c>
-      <c r="G36" s="65"/>
-      <c r="H36" s="65"/>
-      <c r="I36" s="65"/>
-      <c r="J36" s="62" t="s">
+      <c r="G36" s="48"/>
+      <c r="H36" s="48"/>
+      <c r="I36" s="48"/>
+      <c r="J36" s="48" t="s">
         <v>167</v>
       </c>
-      <c r="K36" s="62"/>
-      <c r="L36" s="65"/>
-      <c r="M36" s="65"/>
-      <c r="N36" s="65"/>
-      <c r="O36" s="65"/>
-      <c r="P36" s="65"/>
-      <c r="Q36" s="65"/>
-      <c r="R36" s="65"/>
-      <c r="S36" s="65"/>
-      <c r="T36" s="65"/>
-      <c r="U36" s="65"/>
-      <c r="V36" s="65"/>
-      <c r="W36" s="65"/>
-      <c r="X36" s="65"/>
-      <c r="Y36" s="65"/>
-      <c r="Z36" s="65"/>
-      <c r="AA36" s="65"/>
-      <c r="AB36" s="65"/>
-    </row>
-    <row r="38">
-      <c r="D38" s="3" t="s">
+      <c r="K36" s="48"/>
+      <c r="L36" s="48"/>
+      <c r="M36" s="48"/>
+      <c r="N36" s="48"/>
+      <c r="O36" s="48"/>
+      <c r="P36" s="48"/>
+      <c r="Q36" s="48"/>
+      <c r="R36" s="48"/>
+      <c r="S36" s="48"/>
+      <c r="T36" s="48"/>
+      <c r="U36" s="48"/>
+      <c r="V36" s="48"/>
+      <c r="W36" s="48"/>
+      <c r="X36" s="48"/>
+      <c r="Y36" s="48"/>
+      <c r="Z36" s="48"/>
+      <c r="AA36" s="48"/>
+      <c r="AB36" s="48"/>
+    </row>
+    <row r="38" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="D38" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E38" s="3" t="s">
+      <c r="E38" s="4" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="39">
-      <c r="D39" s="19" t="s">
+    <row r="39" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="D39" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="E39" s="19" t="s">
+      <c r="E39" s="17" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="40">
-      <c r="D40" s="30" t="s">
+    <row r="40" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="D40" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="E40" s="30" t="s">
+      <c r="E40" s="26" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="41">
-      <c r="D41" s="39" t="s">
+    <row r="41" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="D41" s="33" t="s">
         <v>99</v>
       </c>
-      <c r="E41" s="39" t="s">
+      <c r="E41" s="33" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="42">
-      <c r="D42" s="45" t="s">
+    <row r="42" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="D42" s="37" t="s">
         <v>135</v>
       </c>
-      <c r="E42" s="45" t="s">
+      <c r="E42" s="37" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:28" x14ac:dyDescent="0.25">
       <c r="D43" s="9" t="s">
         <v>35</v>
       </c>
@@ -2988,23 +2872,23 @@
         <v>173</v>
       </c>
     </row>
-    <row r="44">
-      <c r="D44" s="66" t="s">
+    <row r="44" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="D44" s="51" t="s">
         <v>41</v>
       </c>
-      <c r="E44" s="66" t="s">
+      <c r="E44" s="51" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="45">
-      <c r="D45" s="67" t="s">
+    <row r="45" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="D45" s="52" t="s">
         <v>64</v>
       </c>
-      <c r="E45" s="67" t="s">
+      <c r="E45" s="52" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:28" x14ac:dyDescent="0.25">
       <c r="D46" s="2" t="s">
         <v>156</v>
       </c>
@@ -3013,69 +2897,69 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="$A$1:$M$36"/>
+  <autoFilter ref="A1:M36" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="I2"/>
-    <hyperlink r:id="rId2" ref="K2"/>
-    <hyperlink r:id="rId3" ref="I3"/>
-    <hyperlink r:id="rId4" ref="K3"/>
-    <hyperlink r:id="rId5" ref="I4"/>
-    <hyperlink r:id="rId6" ref="K4"/>
-    <hyperlink r:id="rId7" ref="I5"/>
-    <hyperlink r:id="rId8" ref="K5"/>
-    <hyperlink r:id="rId9" ref="I6"/>
-    <hyperlink r:id="rId10" ref="K6"/>
-    <hyperlink r:id="rId11" ref="I7"/>
-    <hyperlink r:id="rId12" ref="K7"/>
-    <hyperlink r:id="rId13" ref="I8"/>
-    <hyperlink r:id="rId14" ref="K8"/>
-    <hyperlink r:id="rId15" ref="I9"/>
-    <hyperlink r:id="rId16" ref="K9"/>
-    <hyperlink r:id="rId17" ref="I10"/>
-    <hyperlink r:id="rId18" ref="K10"/>
-    <hyperlink r:id="rId19" ref="I11"/>
-    <hyperlink r:id="rId20" ref="K11"/>
-    <hyperlink r:id="rId21" ref="I12"/>
-    <hyperlink r:id="rId22" ref="K12"/>
-    <hyperlink r:id="rId23" ref="I13"/>
-    <hyperlink r:id="rId24" ref="K13"/>
-    <hyperlink r:id="rId25" ref="I14"/>
-    <hyperlink r:id="rId26" ref="K14"/>
-    <hyperlink r:id="rId27" ref="I15"/>
-    <hyperlink r:id="rId28" ref="K15"/>
-    <hyperlink r:id="rId29" ref="I16"/>
-    <hyperlink r:id="rId30" ref="K16"/>
-    <hyperlink r:id="rId31" ref="I17"/>
-    <hyperlink r:id="rId32" ref="K17"/>
-    <hyperlink r:id="rId33" ref="I18"/>
-    <hyperlink r:id="rId34" ref="K18"/>
-    <hyperlink r:id="rId35" ref="I19"/>
-    <hyperlink r:id="rId36" ref="K19"/>
-    <hyperlink r:id="rId37" ref="I20"/>
-    <hyperlink r:id="rId38" ref="K20"/>
-    <hyperlink r:id="rId39" ref="I21"/>
-    <hyperlink r:id="rId40" ref="K21"/>
-    <hyperlink r:id="rId41" ref="I22"/>
-    <hyperlink r:id="rId42" ref="K22"/>
-    <hyperlink r:id="rId43" ref="I23"/>
-    <hyperlink r:id="rId44" ref="K23"/>
-    <hyperlink r:id="rId45" ref="I24"/>
-    <hyperlink r:id="rId46" ref="K24"/>
-    <hyperlink r:id="rId47" ref="I25"/>
-    <hyperlink r:id="rId48" ref="K25"/>
-    <hyperlink r:id="rId49" ref="I26"/>
-    <hyperlink r:id="rId50" ref="K26"/>
-    <hyperlink r:id="rId51" ref="I27"/>
-    <hyperlink r:id="rId52" ref="K27"/>
-    <hyperlink r:id="rId53" ref="I28"/>
-    <hyperlink r:id="rId54" ref="K28"/>
-    <hyperlink r:id="rId55" ref="I29"/>
-    <hyperlink r:id="rId56" ref="K29"/>
-    <hyperlink r:id="rId57" ref="I30"/>
-    <hyperlink r:id="rId58" ref="K30"/>
-    <hyperlink r:id="rId59" ref="I31"/>
-    <hyperlink r:id="rId60" ref="K31"/>
+    <hyperlink ref="I2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="K2" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="I3" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="K3" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="I4" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="K4" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="I5" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="K5" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="I6" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="K6" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="I7" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="K7" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="I8" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="K8" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="I9" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="K9" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="I10" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="K10" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="I11" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="K11" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="I12" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="K12" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="I13" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="K13" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="I14" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="K14" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="I15" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="K15" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="I16" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="K16" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="I17" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="K17" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="I18" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="K18" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="I19" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="K19" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="I20" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="K20" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="I21" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="K21" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="I22" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="K22" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="I23" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="K23" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="I24" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="K24" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="I25" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="K25" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
+    <hyperlink ref="I26" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="K26" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="I27" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="K27" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="I28" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="K28" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
+    <hyperlink ref="I29" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="K29" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="I30" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="K30" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
+    <hyperlink ref="I31" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
+    <hyperlink ref="K31" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
   </hyperlinks>
-  <drawing r:id="rId61"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>